--- a/consent_forms/034_inheritance_rights_waiver_affidavit--consent_forms.xlsx
+++ b/consent_forms/034_inheritance_rights_waiver_affidavit--consent_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>City Beneficiary Residence</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>State Beneficiary Residence</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Zip Beneficiary Residence</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
